--- a/Paper1/Paper/Data/HawaiiTaxData.xlsx
+++ b/Paper1/Paper/Data/HawaiiTaxData.xlsx
@@ -485,7 +485,7 @@
       <c r="E2" t="n">
         <v>62.62647554806071</v>
       </c>
-      <c r="F2" t="b">
+      <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -510,7 +510,7 @@
       <c r="E3" t="n">
         <v>-22.22637280537916</v>
       </c>
-      <c r="F3" t="b">
+      <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -535,7 +535,7 @@
       <c r="E4" t="n">
         <v>-27.33437663015128</v>
       </c>
-      <c r="F4" t="b">
+      <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -560,7 +560,7 @@
       <c r="E5" t="n">
         <v>-28.61731170708206</v>
       </c>
-      <c r="F5" t="b">
+      <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -585,7 +585,7 @@
       <c r="E6" t="n">
         <v>-11.49269311064718</v>
       </c>
-      <c r="F6" t="b">
+      <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -610,7 +610,7 @@
       <c r="E7" t="n">
         <v>1.339650383924185</v>
       </c>
-      <c r="F7" t="b">
+      <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -635,7 +635,7 @@
       <c r="E8" t="n">
         <v>-0.4036477799372107</v>
       </c>
-      <c r="F8" t="b">
+      <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -660,7 +660,7 @@
       <c r="E9" t="n">
         <v>-23.05456171735242</v>
       </c>
-      <c r="F9" t="b">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -685,7 +685,7 @@
       <c r="E10" t="n">
         <v>14.43973135383527</v>
       </c>
-      <c r="F10" t="b">
+      <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -710,7 +710,7 @@
       <c r="E11" t="n">
         <v>13.67096987752401</v>
       </c>
-      <c r="F11" t="b">
+      <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -735,7 +735,7 @@
       <c r="E12" t="n">
         <v>-27.62981699151912</v>
       </c>
-      <c r="F12" t="b">
+      <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -760,7 +760,7 @@
       <c r="E13" t="n">
         <v>19.78881501759875</v>
       </c>
-      <c r="F13" t="b">
+      <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -785,7 +785,7 @@
       <c r="E14" t="n">
         <v>-12.31367465975373</v>
       </c>
-      <c r="F14" t="b">
+      <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -810,7 +810,7 @@
       <c r="E15" t="n">
         <v>7.636887608069154</v>
       </c>
-      <c r="F15" t="b">
+      <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -835,7 +835,7 @@
       <c r="E16" t="n">
         <v>6.460875807609479</v>
       </c>
-      <c r="F16" t="b">
+      <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -860,7 +860,7 @@
       <c r="E17" t="n">
         <v>84.49943757030371</v>
       </c>
-      <c r="F17" t="b">
+      <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -885,7 +885,7 @@
       <c r="E18" t="n">
         <v>-9.977591697134091</v>
       </c>
-      <c r="F18" t="b">
+      <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -910,7 +910,7 @@
       <c r="E19" t="n">
         <v>-13.57407705948734</v>
       </c>
-      <c r="F19" t="b">
+      <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -935,7 +935,7 @@
       <c r="E20" t="n">
         <v>7.505253677574308</v>
       </c>
-      <c r="F20" t="b">
+      <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -960,7 +960,7 @@
       <c r="E21" t="n">
         <v>-3.06596919500145</v>
       </c>
-      <c r="F21" t="b">
+      <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -985,7 +985,7 @@
       <c r="E22" t="n">
         <v>-14.70270270270271</v>
       </c>
-      <c r="F22" t="b">
+      <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -1010,7 +1010,7 @@
       <c r="E23" t="n">
         <v>-14.21083284799068</v>
       </c>
-      <c r="F23" t="b">
+      <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -1035,7 +1035,7 @@
       <c r="E24" t="n">
         <v>43.95559210526316</v>
       </c>
-      <c r="F24" t="b">
+      <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="E25" t="n">
         <v>6.105125693764291</v>
       </c>
-      <c r="F25" t="b">
+      <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="E26" t="n">
         <v>-28.48484848484848</v>
       </c>
-      <c r="F26" t="b">
+      <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -1110,7 +1110,7 @@
       <c r="E27" t="n">
         <v>18.23590658932024</v>
       </c>
-      <c r="F27" t="b">
+      <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -1135,7 +1135,7 @@
       <c r="E28" t="n">
         <v>9.318948078219824</v>
       </c>
-      <c r="F28" t="b">
+      <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="E29" t="n">
         <v>-18.61968052676503</v>
       </c>
-      <c r="F29" t="b">
+      <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -1185,7 +1185,7 @@
       <c r="E30" t="n">
         <v>11.22756452246822</v>
       </c>
-      <c r="F30" t="b">
+      <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -1210,7 +1210,7 @@
       <c r="E31" t="n">
         <v>2.611453087110616</v>
       </c>
-      <c r="F31" t="b">
+      <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
@@ -1235,7 +1235,7 @@
       <c r="E32" t="n">
         <v>-12.94331192404357</v>
       </c>
-      <c r="F32" t="b">
+      <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
@@ -1260,7 +1260,7 @@
       <c r="E33" t="n">
         <v>-10.17838405036726</v>
       </c>
-      <c r="F33" t="b">
+      <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -1285,7 +1285,7 @@
       <c r="E34" t="n">
         <v>-10.77313054499366</v>
       </c>
-      <c r="F34" t="b">
+      <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -1310,7 +1310,7 @@
       <c r="E35" t="n">
         <v>25.1866938221317</v>
       </c>
-      <c r="F35" t="b">
+      <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -1335,7 +1335,7 @@
       <c r="E36" t="n">
         <v>-21.45101399600114</v>
       </c>
-      <c r="F36" t="b">
+      <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -1360,7 +1360,7 @@
       <c r="E37" t="n">
         <v>-41.29230769230769</v>
       </c>
-      <c r="F37" t="b">
+      <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -1385,7 +1385,7 @@
       <c r="E38" t="n">
         <v>60.02480363786689</v>
       </c>
-      <c r="F38" t="b">
+      <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
@@ -1410,7 +1410,7 @@
       <c r="E39" t="n">
         <v>-13.47339287960749</v>
       </c>
-      <c r="F39" t="b">
+      <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
@@ -1435,7 +1435,7 @@
       <c r="E40" t="n">
         <v>2.245250431778922</v>
       </c>
-      <c r="F40" t="b">
+      <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -1460,7 +1460,7 @@
       <c r="E41" t="n">
         <v>-52.74198381780042</v>
       </c>
-      <c r="F41" t="b">
+      <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -1485,7 +1485,7 @@
       <c r="E42" t="n">
         <v>15.17078916372203</v>
       </c>
-      <c r="F42" t="b">
+      <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -1510,7 +1510,7 @@
       <c r="E43" t="n">
         <v>24.2137793128522</v>
       </c>
-      <c r="F43" t="b">
+      <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
@@ -1535,7 +1535,7 @@
       <c r="E44" t="n">
         <v>-4.298315958299925</v>
       </c>
-      <c r="F44" t="b">
+      <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
@@ -1560,7 +1560,7 @@
       <c r="E45" t="n">
         <v>16.73898531375166</v>
       </c>
-      <c r="F45" t="b">
+      <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -1585,7 +1585,7 @@
       <c r="E46" t="n">
         <v>88.5551948051948</v>
       </c>
-      <c r="F46" t="b">
+      <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -1610,7 +1610,7 @@
       <c r="E47" t="n">
         <v>-4.989154013015185</v>
       </c>
-      <c r="F47" t="b">
+      <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -1635,7 +1635,7 @@
       <c r="E48" t="n">
         <v>36.41818181818181</v>
       </c>
-      <c r="F48" t="b">
+      <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -1660,7 +1660,7 @@
       <c r="E49" t="n">
         <v>84.98427672955975</v>
       </c>
-      <c r="F49" t="b">
+      <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -1685,7 +1685,7 @@
       <c r="E50" t="n">
         <v>6.75536037199691</v>
       </c>
-      <c r="F50" t="b">
+      <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
@@ -1710,7 +1710,7 @@
       <c r="E51" t="n">
         <v>36.17330619366095</v>
       </c>
-      <c r="F51" t="b">
+      <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
@@ -1735,7 +1735,7 @@
       <c r="E52" t="n">
         <v>15.6853281853282</v>
       </c>
-      <c r="F52" t="b">
+      <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
@@ -1760,7 +1760,7 @@
       <c r="E53" t="n">
         <v>146.1636017755231</v>
       </c>
-      <c r="F53" t="b">
+      <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
@@ -1785,7 +1785,7 @@
       <c r="E54" t="n">
         <v>13.86786663939457</v>
       </c>
-      <c r="F54" t="b">
+      <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
@@ -1810,7 +1810,7 @@
       <c r="E55" t="n">
         <v>18.51309819991218</v>
       </c>
-      <c r="F55" t="b">
+      <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
@@ -1835,7 +1835,7 @@
       <c r="E56" t="n">
         <v>43.80760851349086</v>
       </c>
-      <c r="F56" t="b">
+      <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
@@ -1860,7 +1860,7 @@
       <c r="E57" t="n">
         <v>38.68477483917084</v>
       </c>
-      <c r="F57" t="b">
+      <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
@@ -1885,7 +1885,7 @@
       <c r="E58" t="n">
         <v>-10.47137322427895</v>
       </c>
-      <c r="F58" t="b">
+      <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
@@ -1910,7 +1910,7 @@
       <c r="E59" t="n">
         <v>29.16666666666667</v>
       </c>
-      <c r="F59" t="b">
+      <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
@@ -1935,7 +1935,7 @@
       <c r="E60" t="n">
         <v>28.2686925229908</v>
       </c>
-      <c r="F60" t="b">
+      <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
@@ -1960,7 +1960,7 @@
       <c r="E61" t="n">
         <v>-13.23133588326959</v>
       </c>
-      <c r="F61" t="b">
+      <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
@@ -1985,7 +1985,7 @@
       <c r="E62" t="n">
         <v>35.16031457955233</v>
       </c>
-      <c r="F62" t="b">
+      <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
@@ -2010,7 +2010,7 @@
       <c r="E63" t="n">
         <v>5.295750587230419</v>
       </c>
-      <c r="F63" t="b">
+      <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
@@ -2035,7 +2035,7 @@
       <c r="E64" t="n">
         <v>37.25490196078432</v>
       </c>
-      <c r="F64" t="b">
+      <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
@@ -2060,7 +2060,7 @@
       <c r="E65" t="n">
         <v>41.07418856259659</v>
       </c>
-      <c r="F65" t="b">
+      <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
@@ -2085,7 +2085,7 @@
       <c r="E66" t="n">
         <v>8.75696066103826</v>
       </c>
-      <c r="F66" t="b">
+      <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
@@ -2110,7 +2110,7 @@
       <c r="E67" t="n">
         <v>-12.52161027414176</v>
       </c>
-      <c r="F67" t="b">
+      <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
@@ -2135,7 +2135,7 @@
       <c r="E68" t="n">
         <v>28.97098240298332</v>
       </c>
-      <c r="F68" t="b">
+      <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
@@ -2160,7 +2160,7 @@
       <c r="E69" t="n">
         <v>6.504484073806815</v>
       </c>
-      <c r="F69" t="b">
+      <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
@@ -2185,7 +2185,7 @@
       <c r="E70" t="n">
         <v>32.20338983050848</v>
       </c>
-      <c r="F70" t="b">
+      <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="E71" t="n">
         <v>8.793636765355718</v>
       </c>
-      <c r="F71" t="b">
+      <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
@@ -2235,7 +2235,7 @@
       <c r="E72" t="n">
         <v>-16.095178719867</v>
       </c>
-      <c r="F72" t="b">
+      <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
@@ -2260,7 +2260,7 @@
       <c r="E73" t="n">
         <v>52.22857142857143</v>
       </c>
-      <c r="F73" t="b">
+      <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="inlineStr">
@@ -2285,7 +2285,7 @@
       <c r="E74" t="n">
         <v>-9.417241070629313</v>
       </c>
-      <c r="F74" t="b">
+      <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
@@ -2310,7 +2310,7 @@
       <c r="E75" t="n">
         <v>20.37112147637396</v>
       </c>
-      <c r="F75" t="b">
+      <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
@@ -2335,7 +2335,7 @@
       <c r="E76" t="n">
         <v>-23.82978723404256</v>
       </c>
-      <c r="F76" t="b">
+      <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="inlineStr">
@@ -2360,7 +2360,7 @@
       <c r="E77" t="n">
         <v>11.79585501689036</v>
       </c>
-      <c r="F77" t="b">
+      <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
@@ -2385,7 +2385,7 @@
       <c r="E78" t="n">
         <v>-12.445288628293</v>
       </c>
-      <c r="F78" t="b">
+      <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
@@ -2410,7 +2410,7 @@
       <c r="E79" t="n">
         <v>54.58780350084697</v>
       </c>
-      <c r="F79" t="b">
+      <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="inlineStr">
@@ -2435,7 +2435,7 @@
       <c r="E80" t="n">
         <v>-5.005873317068765</v>
       </c>
-      <c r="F80" t="b">
+      <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="inlineStr">
@@ -2460,7 +2460,7 @@
       <c r="E81" t="n">
         <v>-7.704219899341846</v>
       </c>
-      <c r="F81" t="b">
+      <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="inlineStr">
@@ -2485,7 +2485,7 @@
       <c r="E82" t="n">
         <v>7.746863066012</v>
       </c>
-      <c r="F82" t="b">
+      <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
@@ -2510,7 +2510,7 @@
       <c r="E83" t="n">
         <v>6.996344435418367</v>
       </c>
-      <c r="F83" t="b">
+      <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="inlineStr">
@@ -2535,7 +2535,7 @@
       <c r="E84" t="n">
         <v>-4.012383900928795</v>
       </c>
-      <c r="F84" t="b">
+      <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
@@ -2560,7 +2560,7 @@
       <c r="E85" t="n">
         <v>16.81681681681681</v>
       </c>
-      <c r="F85" t="b">
+      <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
@@ -2585,7 +2585,7 @@
       <c r="E86" t="n">
         <v>-20.76292123727641</v>
       </c>
-      <c r="F86" t="b">
+      <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
@@ -2610,7 +2610,7 @@
       <c r="E87" t="n">
         <v>11.29643669446549</v>
       </c>
-      <c r="F87" t="b">
+      <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="inlineStr">
@@ -2635,7 +2635,7 @@
       <c r="E88" t="n">
         <v>27.87310454908221</v>
       </c>
-      <c r="F88" t="b">
+      <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
@@ -2660,7 +2660,7 @@
       <c r="E89" t="n">
         <v>-10.11841567986933</v>
       </c>
-      <c r="F89" t="b">
+      <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
@@ -2685,7 +2685,7 @@
       <c r="E90" t="n">
         <v>-12.39388794567062</v>
       </c>
-      <c r="F90" t="b">
+      <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
@@ -2710,7 +2710,7 @@
       <c r="E91" t="n">
         <v>6.428636654186826</v>
       </c>
-      <c r="F91" t="b">
+      <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
@@ -2735,7 +2735,7 @@
       <c r="E92" t="n">
         <v>-11.69980024731285</v>
       </c>
-      <c r="F92" t="b">
+      <c r="F92" t="n">
         <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
@@ -2760,7 +2760,7 @@
       <c r="E93" t="n">
         <v>18.3619966442953</v>
       </c>
-      <c r="F93" t="b">
+      <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
@@ -2785,7 +2785,7 @@
       <c r="E94" t="n">
         <v>-10.0253164556962</v>
       </c>
-      <c r="F94" t="b">
+      <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="E95" t="n">
         <v>-22.15051722501661</v>
       </c>
-      <c r="F95" t="b">
+      <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
@@ -2835,7 +2835,7 @@
       <c r="E96" t="n">
         <v>28.24151722358405</v>
       </c>
-      <c r="F96" t="b">
+      <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
@@ -2860,7 +2860,7 @@
       <c r="E97" t="n">
         <v>-3.497980168931325</v>
       </c>
-      <c r="F97" t="b">
+      <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
@@ -2885,7 +2885,7 @@
       <c r="E98" t="n">
         <v>-7.171364430032423</v>
       </c>
-      <c r="F98" t="b">
+      <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="inlineStr">
@@ -2910,7 +2910,7 @@
       <c r="E99" t="n">
         <v>-3.564940962761132</v>
       </c>
-      <c r="F99" t="b">
+      <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
@@ -2935,7 +2935,7 @@
       <c r="E100" t="n">
         <v>32.89904821344984</v>
       </c>
-      <c r="F100" t="b">
+      <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
@@ -2960,7 +2960,7 @@
       <c r="E101" t="n">
         <v>22.35144466654553</v>
       </c>
-      <c r="F101" t="b">
+      <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
@@ -2985,7 +2985,7 @@
       <c r="E102" t="n">
         <v>31.21231696813091</v>
       </c>
-      <c r="F102" t="b">
+      <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
@@ -3010,7 +3010,7 @@
       <c r="E103" t="n">
         <v>18.18961818961819</v>
       </c>
-      <c r="F103" t="b">
+      <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
@@ -3035,7 +3035,7 @@
       <c r="E104" t="n">
         <v>1.885166433265106</v>
       </c>
-      <c r="F104" t="b">
+      <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
@@ -3060,7 +3060,7 @@
       <c r="E105" t="n">
         <v>48.91468060600693</v>
       </c>
-      <c r="F105" t="b">
+      <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
@@ -3085,7 +3085,7 @@
       <c r="E106" t="n">
         <v>35.99699868692554</v>
       </c>
-      <c r="F106" t="b">
+      <c r="F106" t="n">
         <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
@@ -3110,7 +3110,7 @@
       <c r="E107" t="n">
         <v>22.50396196513471</v>
       </c>
-      <c r="F107" t="b">
+      <c r="F107" t="n">
         <v>0</v>
       </c>
       <c r="G107" t="inlineStr">
@@ -3135,7 +3135,7 @@
       <c r="E108" t="n">
         <v>62.19315895372232</v>
       </c>
-      <c r="F108" t="b">
+      <c r="F108" t="n">
         <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
@@ -3160,7 +3160,7 @@
       <c r="E109" t="n">
         <v>-6.945105127961182</v>
       </c>
-      <c r="F109" t="b">
+      <c r="F109" t="n">
         <v>0</v>
       </c>
       <c r="G109" t="inlineStr">
@@ -3185,7 +3185,7 @@
       <c r="E110" t="n">
         <v>90.71610909579471</v>
       </c>
-      <c r="F110" t="b">
+      <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
@@ -3210,7 +3210,7 @@
       <c r="E111" t="n">
         <v>25.77505690291186</v>
       </c>
-      <c r="F111" t="b">
+      <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="inlineStr">
@@ -3235,7 +3235,7 @@
       <c r="E112" t="n">
         <v>-6.099207513941884</v>
       </c>
-      <c r="F112" t="b">
+      <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
@@ -3260,7 +3260,7 @@
       <c r="E113" t="n">
         <v>-12.46101292143176</v>
       </c>
-      <c r="F113" t="b">
+      <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="inlineStr">
@@ -3285,7 +3285,7 @@
       <c r="E114" t="n">
         <v>64.93804874046114</v>
       </c>
-      <c r="F114" t="b">
+      <c r="F114" t="n">
         <v>0</v>
       </c>
       <c r="G114" t="inlineStr">
@@ -3310,7 +3310,7 @@
       <c r="E115" t="n">
         <v>-0.2395644283121556</v>
       </c>
-      <c r="F115" t="b">
+      <c r="F115" t="n">
         <v>0</v>
       </c>
       <c r="G115" t="inlineStr">
@@ -3335,7 +3335,7 @@
       <c r="E116" t="n">
         <v>45.54874180587862</v>
       </c>
-      <c r="F116" t="b">
+      <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
@@ -3360,7 +3360,7 @@
       <c r="E117" t="n">
         <v>5.086863398381714</v>
       </c>
-      <c r="F117" t="b">
+      <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="inlineStr">
@@ -3385,7 +3385,7 @@
       <c r="E118" t="n">
         <v>-27.4551724137931</v>
       </c>
-      <c r="F118" t="b">
+      <c r="F118" t="n">
         <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
@@ -3410,7 +3410,7 @@
       <c r="E119" t="n">
         <v>71.85789630809036</v>
       </c>
-      <c r="F119" t="b">
+      <c r="F119" t="n">
         <v>0</v>
       </c>
       <c r="G119" t="inlineStr">
@@ -3435,7 +3435,7 @@
       <c r="E120" t="n">
         <v>-6.09725840466443</v>
       </c>
-      <c r="F120" t="b">
+      <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="inlineStr">
@@ -3460,7 +3460,7 @@
       <c r="E121" t="n">
         <v>-6.389939678969425</v>
       </c>
-      <c r="F121" t="b">
+      <c r="F121" t="n">
         <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
@@ -3485,7 +3485,7 @@
       <c r="E122" t="n">
         <v>19.90841845720324</v>
       </c>
-      <c r="F122" t="b">
+      <c r="F122" t="n">
         <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
@@ -3510,7 +3510,7 @@
       <c r="E123" t="n">
         <v>14.05928237129486</v>
       </c>
-      <c r="F123" t="b">
+      <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="inlineStr">
@@ -3535,7 +3535,7 @@
       <c r="E124" t="n">
         <v>-24.1997999499875</v>
       </c>
-      <c r="F124" t="b">
+      <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="inlineStr">
@@ -3560,7 +3560,7 @@
       <c r="E125" t="n">
         <v>62.78418730912794</v>
       </c>
-      <c r="F125" t="b">
+      <c r="F125" t="n">
         <v>0</v>
       </c>
       <c r="G125" t="inlineStr">
@@ -3585,7 +3585,7 @@
       <c r="E126" t="n">
         <v>-17.75036067857321</v>
       </c>
-      <c r="F126" t="b">
+      <c r="F126" t="n">
         <v>0</v>
       </c>
       <c r="G126" t="inlineStr">
@@ -3610,7 +3610,7 @@
       <c r="E127" t="n">
         <v>-23.54096929122399</v>
       </c>
-      <c r="F127" t="b">
+      <c r="F127" t="n">
         <v>0</v>
       </c>
       <c r="G127" t="inlineStr">
@@ -3635,7 +3635,7 @@
       <c r="E128" t="n">
         <v>18.41493534795875</v>
       </c>
-      <c r="F128" t="b">
+      <c r="F128" t="n">
         <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
@@ -3660,7 +3660,7 @@
       <c r="E129" t="n">
         <v>-5.123704919889038</v>
       </c>
-      <c r="F129" t="b">
+      <c r="F129" t="n">
         <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
@@ -3685,7 +3685,7 @@
       <c r="E130" t="n">
         <v>12.56773457553</v>
       </c>
-      <c r="F130" t="b">
+      <c r="F130" t="n">
         <v>0</v>
       </c>
       <c r="G130" t="inlineStr">
@@ -3710,7 +3710,7 @@
       <c r="E131" t="n">
         <v>-9.976838448176029</v>
       </c>
-      <c r="F131" t="b">
+      <c r="F131" t="n">
         <v>0</v>
       </c>
       <c r="G131" t="inlineStr">
@@ -3735,7 +3735,7 @@
       <c r="E132" t="n">
         <v>-25.41779509875157</v>
       </c>
-      <c r="F132" t="b">
+      <c r="F132" t="n">
         <v>0</v>
       </c>
       <c r="G132" t="inlineStr">
@@ -3760,7 +3760,7 @@
       <c r="E133" t="n">
         <v>0.6006989951944153</v>
       </c>
-      <c r="F133" t="b">
+      <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="inlineStr">
@@ -3785,7 +3785,7 @@
       <c r="E134" t="n">
         <v>-30.27436695846307</v>
       </c>
-      <c r="F134" t="b">
+      <c r="F134" t="n">
         <v>0</v>
       </c>
       <c r="G134" t="inlineStr">
@@ -3810,7 +3810,7 @@
       <c r="E135" t="n">
         <v>-22.29456176824598</v>
       </c>
-      <c r="F135" t="b">
+      <c r="F135" t="n">
         <v>0</v>
       </c>
       <c r="G135" t="inlineStr">
@@ -3835,7 +3835,7 @@
       <c r="E136" t="n">
         <v>-18.77938144329897</v>
       </c>
-      <c r="F136" t="b">
+      <c r="F136" t="n">
         <v>0</v>
       </c>
       <c r="G136" t="inlineStr">
@@ -3860,7 +3860,7 @@
       <c r="E137" t="n">
         <v>-6.644431705664699</v>
       </c>
-      <c r="F137" t="b">
+      <c r="F137" t="n">
         <v>0</v>
       </c>
       <c r="G137" t="inlineStr">
@@ -3885,7 +3885,7 @@
       <c r="E138" t="n">
         <v>-10.7905401318575</v>
       </c>
-      <c r="F138" t="b">
+      <c r="F138" t="n">
         <v>0</v>
       </c>
       <c r="G138" t="inlineStr">
@@ -3910,7 +3910,7 @@
       <c r="E139" t="n">
         <v>-22.87998477205673</v>
       </c>
-      <c r="F139" t="b">
+      <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="inlineStr">
@@ -3935,7 +3935,7 @@
       <c r="E140" t="n">
         <v>6.564014477639413</v>
       </c>
-      <c r="F140" t="b">
+      <c r="F140" t="n">
         <v>0</v>
       </c>
       <c r="G140" t="inlineStr">
@@ -3960,7 +3960,7 @@
       <c r="E141" t="n">
         <v>-27.2407208497434</v>
       </c>
-      <c r="F141" t="b">
+      <c r="F141" t="n">
         <v>0</v>
       </c>
       <c r="G141" t="inlineStr">
@@ -3985,7 +3985,7 @@
       <c r="E142" t="n">
         <v>57.36846550122456</v>
       </c>
-      <c r="F142" t="b">
+      <c r="F142" t="n">
         <v>0</v>
       </c>
       <c r="G142" t="inlineStr">
@@ -4010,7 +4010,7 @@
       <c r="E143" t="n">
         <v>-22.58956711905834</v>
       </c>
-      <c r="F143" t="b">
+      <c r="F143" t="n">
         <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
@@ -4035,7 +4035,7 @@
       <c r="E144" t="n">
         <v>-9.361438313701175</v>
       </c>
-      <c r="F144" t="b">
+      <c r="F144" t="n">
         <v>0</v>
       </c>
       <c r="G144" t="inlineStr">
@@ -4060,7 +4060,7 @@
       <c r="E145" t="n">
         <v>57.21420041255021</v>
       </c>
-      <c r="F145" t="b">
+      <c r="F145" t="n">
         <v>0</v>
       </c>
       <c r="G145" t="inlineStr">
@@ -4085,7 +4085,7 @@
       <c r="E146" t="n">
         <v>15.37748567576678</v>
       </c>
-      <c r="F146" t="b">
+      <c r="F146" t="n">
         <v>0</v>
       </c>
       <c r="G146" t="inlineStr">
@@ -4110,7 +4110,7 @@
       <c r="E147" t="n">
         <v>15.36999225515736</v>
       </c>
-      <c r="F147" t="b">
+      <c r="F147" t="n">
         <v>0</v>
       </c>
       <c r="G147" t="inlineStr">
@@ -4135,7 +4135,7 @@
       <c r="E148" t="n">
         <v>41.74451665312753</v>
       </c>
-      <c r="F148" t="b">
+      <c r="F148" t="n">
         <v>0</v>
       </c>
       <c r="G148" t="inlineStr">
@@ -4160,7 +4160,7 @@
       <c r="E149" t="n">
         <v>-22.4740426482081</v>
       </c>
-      <c r="F149" t="b">
+      <c r="F149" t="n">
         <v>0</v>
       </c>
       <c r="G149" t="inlineStr">
@@ -4185,7 +4185,7 @@
       <c r="E150" t="n">
         <v>-4.773204963048339</v>
       </c>
-      <c r="F150" t="b">
+      <c r="F150" t="n">
         <v>0</v>
       </c>
       <c r="G150" t="inlineStr">
@@ -4210,7 +4210,7 @@
       <c r="E151" t="n">
         <v>72.09675428853511</v>
       </c>
-      <c r="F151" t="b">
+      <c r="F151" t="n">
         <v>0</v>
       </c>
       <c r="G151" t="inlineStr">
@@ -4235,7 +4235,7 @@
       <c r="E152" t="n">
         <v>-27.1486961026999</v>
       </c>
-      <c r="F152" t="b">
+      <c r="F152" t="n">
         <v>0</v>
       </c>
       <c r="G152" t="inlineStr">
@@ -4260,7 +4260,7 @@
       <c r="E153" t="n">
         <v>21.03666037890592</v>
       </c>
-      <c r="F153" t="b">
+      <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="inlineStr">
@@ -4285,7 +4285,7 @@
       <c r="E154" t="n">
         <v>4.051733390576362</v>
       </c>
-      <c r="F154" t="b">
+      <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="inlineStr">
@@ -4310,7 +4310,7 @@
       <c r="E155" t="n">
         <v>6.730369754881593</v>
       </c>
-      <c r="F155" t="b">
+      <c r="F155" t="n">
         <v>0</v>
       </c>
       <c r="G155" t="inlineStr">
@@ -4335,7 +4335,7 @@
       <c r="E156" t="n">
         <v>-2.970490521790115</v>
       </c>
-      <c r="F156" t="b">
+      <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="inlineStr">
@@ -4360,7 +4360,7 @@
       <c r="E157" t="n">
         <v>4.882259512464615</v>
       </c>
-      <c r="F157" t="b">
+      <c r="F157" t="n">
         <v>0</v>
       </c>
       <c r="G157" t="inlineStr">
@@ -4385,7 +4385,7 @@
       <c r="E158" t="n">
         <v>-11.86737749214928</v>
       </c>
-      <c r="F158" t="b">
+      <c r="F158" t="n">
         <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
@@ -4410,7 +4410,7 @@
       <c r="E159" t="n">
         <v>11.4793116074698</v>
       </c>
-      <c r="F159" t="b">
+      <c r="F159" t="n">
         <v>0</v>
       </c>
       <c r="G159" t="inlineStr">
@@ -4435,7 +4435,7 @@
       <c r="E160" t="n">
         <v>42.33827638082956</v>
       </c>
-      <c r="F160" t="b">
+      <c r="F160" t="n">
         <v>0</v>
       </c>
       <c r="G160" t="inlineStr">
@@ -4460,7 +4460,7 @@
       <c r="E161" t="n">
         <v>16.93548387096775</v>
       </c>
-      <c r="F161" t="b">
+      <c r="F161" t="n">
         <v>0</v>
       </c>
       <c r="G161" t="inlineStr">
@@ -4485,7 +4485,7 @@
       <c r="E162" t="n">
         <v>-0.7191171235315097</v>
       </c>
-      <c r="F162" t="b">
+      <c r="F162" t="n">
         <v>0</v>
       </c>
       <c r="G162" t="inlineStr">
@@ -4510,7 +4510,7 @@
       <c r="E163" t="n">
         <v>19.72032986733596</v>
       </c>
-      <c r="F163" t="b">
+      <c r="F163" t="n">
         <v>0</v>
       </c>
       <c r="G163" t="inlineStr">
@@ -4535,7 +4535,7 @@
       <c r="E164" t="n">
         <v>-15.57487159225602</v>
       </c>
-      <c r="F164" t="b">
+      <c r="F164" t="n">
         <v>0</v>
       </c>
       <c r="G164" t="inlineStr">
@@ -4560,7 +4560,7 @@
       <c r="E165" t="n">
         <v>61.85797533541131</v>
       </c>
-      <c r="F165" t="b">
+      <c r="F165" t="n">
         <v>0</v>
       </c>
       <c r="G165" t="inlineStr">
@@ -4585,7 +4585,7 @@
       <c r="E166" t="n">
         <v>-3.20800453865594</v>
       </c>
-      <c r="F166" t="b">
+      <c r="F166" t="n">
         <v>0</v>
       </c>
       <c r="G166" t="inlineStr">
@@ -4610,7 +4610,7 @@
       <c r="E167" t="n">
         <v>-3.73686259244842</v>
       </c>
-      <c r="F167" t="b">
+      <c r="F167" t="n">
         <v>0</v>
       </c>
       <c r="G167" t="inlineStr">
@@ -4635,7 +4635,7 @@
       <c r="E168" t="n">
         <v>87.59315206445115</v>
       </c>
-      <c r="F168" t="b">
+      <c r="F168" t="n">
         <v>0</v>
       </c>
       <c r="G168" t="inlineStr">
@@ -4660,7 +4660,7 @@
       <c r="E169" t="n">
         <v>-44.06768501448512</v>
       </c>
-      <c r="F169" t="b">
+      <c r="F169" t="n">
         <v>0</v>
       </c>
       <c r="G169" t="inlineStr">
@@ -4685,7 +4685,7 @@
       <c r="E170" t="n">
         <v>47.77096453430561</v>
       </c>
-      <c r="F170" t="b">
+      <c r="F170" t="n">
         <v>0</v>
       </c>
       <c r="G170" t="inlineStr">
@@ -4710,7 +4710,7 @@
       <c r="E171" t="n">
         <v>-1.538293096841303</v>
       </c>
-      <c r="F171" t="b">
+      <c r="F171" t="n">
         <v>0</v>
       </c>
       <c r="G171" t="inlineStr">
@@ -4735,7 +4735,7 @@
       <c r="E172" t="n">
         <v>-5.556394383210028</v>
       </c>
-      <c r="F172" t="b">
+      <c r="F172" t="n">
         <v>0</v>
       </c>
       <c r="G172" t="inlineStr">
@@ -4760,7 +4760,7 @@
       <c r="E173" t="n">
         <v>-2.795566502463054</v>
       </c>
-      <c r="F173" t="b">
+      <c r="F173" t="n">
         <v>0</v>
       </c>
       <c r="G173" t="inlineStr">
@@ -4785,7 +4785,7 @@
       <c r="E174" t="n">
         <v>22.85570854847963</v>
       </c>
-      <c r="F174" t="b">
+      <c r="F174" t="n">
         <v>0</v>
       </c>
       <c r="G174" t="inlineStr">
@@ -4810,7 +4810,7 @@
       <c r="E175" t="n">
         <v>10.50613956274333</v>
       </c>
-      <c r="F175" t="b">
+      <c r="F175" t="n">
         <v>0</v>
       </c>
       <c r="G175" t="inlineStr">
@@ -4835,7 +4835,7 @@
       <c r="E176" t="n">
         <v>54.67053538000748</v>
       </c>
-      <c r="F176" t="b">
+      <c r="F176" t="n">
         <v>0</v>
       </c>
       <c r="G176" t="inlineStr">
@@ -4860,7 +4860,7 @@
       <c r="E177" t="n">
         <v>-11.87256666806212</v>
       </c>
-      <c r="F177" t="b">
+      <c r="F177" t="n">
         <v>0</v>
       </c>
       <c r="G177" t="inlineStr">
@@ -4885,7 +4885,7 @@
       <c r="E178" t="n">
         <v>-5.126019076037725</v>
       </c>
-      <c r="F178" t="b">
+      <c r="F178" t="n">
         <v>0</v>
       </c>
       <c r="G178" t="inlineStr">
@@ -4910,7 +4910,7 @@
       <c r="E179" t="n">
         <v>16.37687019813992</v>
       </c>
-      <c r="F179" t="b">
+      <c r="F179" t="n">
         <v>0</v>
       </c>
       <c r="G179" t="inlineStr">
@@ -4935,7 +4935,7 @@
       <c r="E180" t="n">
         <v>10.19433111445136</v>
       </c>
-      <c r="F180" t="b">
+      <c r="F180" t="n">
         <v>0</v>
       </c>
       <c r="G180" t="inlineStr">
@@ -4960,7 +4960,7 @@
       <c r="E181" t="n">
         <v>31.06533254855797</v>
       </c>
-      <c r="F181" t="b">
+      <c r="F181" t="n">
         <v>0</v>
       </c>
       <c r="G181" t="inlineStr">
@@ -4985,7 +4985,7 @@
       <c r="E182" t="n">
         <v>9.162788089496999</v>
       </c>
-      <c r="F182" t="b">
+      <c r="F182" t="n">
         <v>0</v>
       </c>
       <c r="G182" t="inlineStr">
@@ -5010,7 +5010,7 @@
       <c r="E183" t="n">
         <v>19.93772934504614</v>
       </c>
-      <c r="F183" t="b">
+      <c r="F183" t="n">
         <v>0</v>
       </c>
       <c r="G183" t="inlineStr">
@@ -5035,7 +5035,7 @@
       <c r="E184" t="n">
         <v>-0.5648814281907777</v>
       </c>
-      <c r="F184" t="b">
+      <c r="F184" t="n">
         <v>0</v>
       </c>
       <c r="G184" t="inlineStr">
@@ -5060,7 +5060,7 @@
       <c r="E185" t="n">
         <v>-5.150133029266435</v>
       </c>
-      <c r="F185" t="b">
+      <c r="F185" t="n">
         <v>0</v>
       </c>
       <c r="G185" t="inlineStr">
@@ -5085,7 +5085,7 @@
       <c r="E186" t="n">
         <v>38.39822543926215</v>
       </c>
-      <c r="F186" t="b">
+      <c r="F186" t="n">
         <v>0</v>
       </c>
       <c r="G186" t="inlineStr">
@@ -5110,7 +5110,7 @@
       <c r="E187" t="n">
         <v>-6.856740202721012</v>
       </c>
-      <c r="F187" t="b">
+      <c r="F187" t="n">
         <v>0</v>
       </c>
       <c r="G187" t="inlineStr">
@@ -5135,7 +5135,7 @@
       <c r="E188" t="n">
         <v>5.639939485627843</v>
       </c>
-      <c r="F188" t="b">
+      <c r="F188" t="n">
         <v>0</v>
       </c>
       <c r="G188" t="inlineStr">
@@ -5160,7 +5160,7 @@
       <c r="E189" t="n">
         <v>14.61213244026411</v>
       </c>
-      <c r="F189" t="b">
+      <c r="F189" t="n">
         <v>0</v>
       </c>
       <c r="G189" t="inlineStr">
@@ -5185,7 +5185,7 @@
       <c r="E190" t="n">
         <v>-14.64195450716091</v>
       </c>
-      <c r="F190" t="b">
+      <c r="F190" t="n">
         <v>0</v>
       </c>
       <c r="G190" t="inlineStr">
@@ -5210,7 +5210,7 @@
       <c r="E191" t="n">
         <v>44.58651841556636</v>
       </c>
-      <c r="F191" t="b">
+      <c r="F191" t="n">
         <v>0</v>
       </c>
       <c r="G191" t="inlineStr">
@@ -5235,7 +5235,7 @@
       <c r="E192" t="n">
         <v>-24.34841915525893</v>
       </c>
-      <c r="F192" t="b">
+      <c r="F192" t="n">
         <v>0</v>
       </c>
       <c r="G192" t="inlineStr">
@@ -5260,7 +5260,7 @@
       <c r="E193" t="n">
         <v>6.601401113705774</v>
       </c>
-      <c r="F193" t="b">
+      <c r="F193" t="n">
         <v>0</v>
       </c>
       <c r="G193" t="inlineStr">
@@ -5285,7 +5285,7 @@
       <c r="E194" t="n">
         <v>13.48435814455231</v>
       </c>
-      <c r="F194" t="b">
+      <c r="F194" t="n">
         <v>0</v>
       </c>
       <c r="G194" t="inlineStr">
@@ -5310,7 +5310,7 @@
       <c r="E195" t="n">
         <v>-6.332282588540705</v>
       </c>
-      <c r="F195" t="b">
+      <c r="F195" t="n">
         <v>0</v>
       </c>
       <c r="G195" t="inlineStr">
@@ -5335,7 +5335,7 @@
       <c r="E196" t="n">
         <v>-25.70341390213838</v>
       </c>
-      <c r="F196" t="b">
+      <c r="F196" t="n">
         <v>0</v>
       </c>
       <c r="G196" t="inlineStr">
@@ -5360,7 +5360,7 @@
       <c r="E197" t="n">
         <v>33.09957924263676</v>
       </c>
-      <c r="F197" t="b">
+      <c r="F197" t="n">
         <v>0</v>
       </c>
       <c r="G197" t="inlineStr">
@@ -5385,7 +5385,7 @@
       <c r="E198" t="n">
         <v>9.840145092580887</v>
       </c>
-      <c r="F198" t="b">
+      <c r="F198" t="n">
         <v>0</v>
       </c>
       <c r="G198" t="inlineStr">
@@ -5410,7 +5410,7 @@
       <c r="E199" t="n">
         <v>3.660381750465547</v>
       </c>
-      <c r="F199" t="b">
+      <c r="F199" t="n">
         <v>0</v>
       </c>
       <c r="G199" t="inlineStr">
@@ -5435,7 +5435,7 @@
       <c r="E200" t="n">
         <v>10.56882625880735</v>
       </c>
-      <c r="F200" t="b">
+      <c r="F200" t="n">
         <v>0</v>
       </c>
       <c r="G200" t="inlineStr">
@@ -5460,7 +5460,7 @@
       <c r="E201" t="n">
         <v>1.744933062544041</v>
       </c>
-      <c r="F201" t="b">
+      <c r="F201" t="n">
         <v>0</v>
       </c>
       <c r="G201" t="inlineStr">
@@ -5485,7 +5485,7 @@
       <c r="E202" t="n">
         <v>-2.118699828924864</v>
       </c>
-      <c r="F202" t="b">
+      <c r="F202" t="n">
         <v>0</v>
       </c>
       <c r="G202" t="inlineStr">
@@ -5510,7 +5510,7 @@
       <c r="E203" t="n">
         <v>9.425165817552639</v>
       </c>
-      <c r="F203" t="b">
+      <c r="F203" t="n">
         <v>0</v>
       </c>
       <c r="G203" t="inlineStr">
@@ -5535,7 +5535,7 @@
       <c r="E204" t="n">
         <v>12.57646983063945</v>
       </c>
-      <c r="F204" t="b">
+      <c r="F204" t="n">
         <v>0</v>
       </c>
       <c r="G204" t="inlineStr">
@@ -5560,7 +5560,7 @@
       <c r="E205" t="n">
         <v>14.76956778161598</v>
       </c>
-      <c r="F205" t="b">
+      <c r="F205" t="n">
         <v>0</v>
       </c>
       <c r="G205" t="inlineStr">
@@ -5585,7 +5585,7 @@
       <c r="E206" t="n">
         <v>-14.97374615245338</v>
       </c>
-      <c r="F206" t="b">
+      <c r="F206" t="n">
         <v>0</v>
       </c>
       <c r="G206" t="inlineStr">
@@ -5610,7 +5610,7 @@
       <c r="E207" t="n">
         <v>17.79669405127189</v>
       </c>
-      <c r="F207" t="b">
+      <c r="F207" t="n">
         <v>0</v>
       </c>
       <c r="G207" t="inlineStr">
@@ -5635,7 +5635,7 @@
       <c r="E208" t="n">
         <v>39.70280603044074</v>
       </c>
-      <c r="F208" t="b">
+      <c r="F208" t="n">
         <v>0</v>
       </c>
       <c r="G208" t="inlineStr">
@@ -5660,7 +5660,7 @@
       <c r="E209" t="n">
         <v>1.23939986953685</v>
       </c>
-      <c r="F209" t="b">
+      <c r="F209" t="n">
         <v>0</v>
       </c>
       <c r="G209" t="inlineStr">
@@ -5685,7 +5685,7 @@
       <c r="E210" t="n">
         <v>-35.99569925504954</v>
       </c>
-      <c r="F210" t="b">
+      <c r="F210" t="n">
         <v>0</v>
       </c>
       <c r="G210" t="inlineStr">
@@ -5710,7 +5710,7 @@
       <c r="E211" t="n">
         <v>0.9655869308931697</v>
       </c>
-      <c r="F211" t="b">
+      <c r="F211" t="n">
         <v>0</v>
       </c>
       <c r="G211" t="inlineStr">
@@ -5735,7 +5735,7 @@
       <c r="E212" t="n">
         <v>-2.310641384312506</v>
       </c>
-      <c r="F212" t="b">
+      <c r="F212" t="n">
         <v>0</v>
       </c>
       <c r="G212" t="inlineStr">
@@ -5760,7 +5760,7 @@
       <c r="E213" t="n">
         <v>-28.32002607137037</v>
       </c>
-      <c r="F213" t="b">
+      <c r="F213" t="n">
         <v>0</v>
       </c>
       <c r="G213" t="inlineStr">
@@ -5785,7 +5785,7 @@
       <c r="E214" t="n">
         <v>55.87523527830063</v>
       </c>
-      <c r="F214" t="b">
+      <c r="F214" t="n">
         <v>0</v>
       </c>
       <c r="G214" t="inlineStr">
@@ -5810,7 +5810,7 @@
       <c r="E215" t="n">
         <v>-28.74774893486186</v>
       </c>
-      <c r="F215" t="b">
+      <c r="F215" t="n">
         <v>0</v>
       </c>
       <c r="G215" t="inlineStr">
@@ -5835,7 +5835,7 @@
       <c r="E216" t="n">
         <v>-14.42626701750371</v>
       </c>
-      <c r="F216" t="b">
+      <c r="F216" t="n">
         <v>0</v>
       </c>
       <c r="G216" t="inlineStr">
@@ -5860,7 +5860,7 @@
       <c r="E217" t="n">
         <v>21.26706797827045</v>
       </c>
-      <c r="F217" t="b">
+      <c r="F217" t="n">
         <v>0</v>
       </c>
       <c r="G217" t="inlineStr">
@@ -5885,7 +5885,7 @@
       <c r="E218" t="n">
         <v>-27.62989778534923</v>
       </c>
-      <c r="F218" t="b">
+      <c r="F218" t="n">
         <v>0</v>
       </c>
       <c r="G218" t="inlineStr">
@@ -5910,7 +5910,7 @@
       <c r="E219" t="n">
         <v>-15.91042769515166</v>
       </c>
-      <c r="F219" t="b">
+      <c r="F219" t="n">
         <v>0</v>
       </c>
       <c r="G219" t="inlineStr">
@@ -5935,7 +5935,7 @@
       <c r="E220" t="n">
         <v>-3.950018071978112</v>
       </c>
-      <c r="F220" t="b">
+      <c r="F220" t="n">
         <v>0</v>
       </c>
       <c r="G220" t="inlineStr">
@@ -5960,7 +5960,7 @@
       <c r="E221" t="n">
         <v>-16.69805709754163</v>
       </c>
-      <c r="F221" t="b">
+      <c r="F221" t="n">
         <v>0</v>
       </c>
       <c r="G221" t="inlineStr">
@@ -5985,7 +5985,7 @@
       <c r="E222" t="n">
         <v>-13.99088072954163</v>
       </c>
-      <c r="F222" t="b">
+      <c r="F222" t="n">
         <v>0</v>
       </c>
       <c r="G222" t="inlineStr">
@@ -6010,7 +6010,7 @@
       <c r="E223" t="n">
         <v>10.75340561579095</v>
       </c>
-      <c r="F223" t="b">
+      <c r="F223" t="n">
         <v>0</v>
       </c>
       <c r="G223" t="inlineStr">
@@ -6035,7 +6035,7 @@
       <c r="E224" t="n">
         <v>-21.98239287229529</v>
       </c>
-      <c r="F224" t="b">
+      <c r="F224" t="n">
         <v>0</v>
       </c>
       <c r="G224" t="inlineStr">
@@ -6060,7 +6060,7 @@
       <c r="E225" t="n">
         <v>15.30461468515572</v>
       </c>
-      <c r="F225" t="b">
+      <c r="F225" t="n">
         <v>0</v>
       </c>
       <c r="G225" t="inlineStr">
@@ -6085,7 +6085,7 @@
       <c r="E226" t="n">
         <v>-24.45230291530101</v>
       </c>
-      <c r="F226" t="b">
+      <c r="F226" t="n">
         <v>0</v>
       </c>
       <c r="G226" t="inlineStr">
@@ -6110,7 +6110,7 @@
       <c r="E227" t="n">
         <v>-16.27419553692516</v>
       </c>
-      <c r="F227" t="b">
+      <c r="F227" t="n">
         <v>0</v>
       </c>
       <c r="G227" t="inlineStr">
@@ -6135,7 +6135,7 @@
       <c r="E228" t="n">
         <v>26.35695187165776</v>
       </c>
-      <c r="F228" t="b">
+      <c r="F228" t="n">
         <v>0</v>
       </c>
       <c r="G228" t="inlineStr">
@@ -6160,7 +6160,7 @@
       <c r="E229" t="n">
         <v>45.27513772020097</v>
       </c>
-      <c r="F229" t="b">
+      <c r="F229" t="n">
         <v>0</v>
       </c>
       <c r="G229" t="inlineStr">
@@ -6185,7 +6185,7 @@
       <c r="E230" t="n">
         <v>15.16845667206119</v>
       </c>
-      <c r="F230" t="b">
+      <c r="F230" t="n">
         <v>0</v>
       </c>
       <c r="G230" t="inlineStr">
@@ -6210,7 +6210,7 @@
       <c r="E231" t="n">
         <v>-3.142643017736702</v>
       </c>
-      <c r="F231" t="b">
+      <c r="F231" t="n">
         <v>0</v>
       </c>
       <c r="G231" t="inlineStr">
@@ -6235,7 +6235,7 @@
       <c r="E232" t="n">
         <v>26.8143210407483</v>
       </c>
-      <c r="F232" t="b">
+      <c r="F232" t="n">
         <v>0</v>
       </c>
       <c r="G232" t="inlineStr">
@@ -6260,7 +6260,7 @@
       <c r="E233" t="n">
         <v>24.2339501398227</v>
       </c>
-      <c r="F233" t="b">
+      <c r="F233" t="n">
         <v>0</v>
       </c>
       <c r="G233" t="inlineStr">
@@ -6285,7 +6285,7 @@
       <c r="E234" t="n">
         <v>17.32003348214286</v>
       </c>
-      <c r="F234" t="b">
+      <c r="F234" t="n">
         <v>0</v>
       </c>
       <c r="G234" t="inlineStr">
@@ -6310,7 +6310,7 @@
       <c r="E235" t="n">
         <v>-5.060495004769317</v>
       </c>
-      <c r="F235" t="b">
+      <c r="F235" t="n">
         <v>0</v>
       </c>
       <c r="G235" t="inlineStr">
@@ -6335,7 +6335,7 @@
       <c r="E236" t="n">
         <v>4.350486030861256</v>
       </c>
-      <c r="F236" t="b">
+      <c r="F236" t="n">
         <v>0</v>
       </c>
       <c r="G236" t="inlineStr">
@@ -6360,7 +6360,7 @@
       <c r="E237" t="n">
         <v>39.68652964660653</v>
       </c>
-      <c r="F237" t="b">
+      <c r="F237" t="n">
         <v>0</v>
       </c>
       <c r="G237" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="E238" t="n">
         <v>47.99634661491037</v>
       </c>
-      <c r="F238" t="b">
+      <c r="F238" t="n">
         <v>0</v>
       </c>
       <c r="G238" t="inlineStr">
@@ -6410,7 +6410,7 @@
       <c r="E239" t="n">
         <v>21.63157119717274</v>
       </c>
-      <c r="F239" t="b">
+      <c r="F239" t="n">
         <v>0</v>
       </c>
       <c r="G239" t="inlineStr">
@@ -6435,7 +6435,7 @@
       <c r="E240" t="n">
         <v>24.92197005766281</v>
       </c>
-      <c r="F240" t="b">
+      <c r="F240" t="n">
         <v>0</v>
       </c>
       <c r="G240" t="inlineStr">
@@ -6460,7 +6460,7 @@
       <c r="E241" t="n">
         <v>-22.62688557379782</v>
       </c>
-      <c r="F241" t="b">
+      <c r="F241" t="n">
         <v>0</v>
       </c>
       <c r="G241" t="inlineStr">
@@ -6485,7 +6485,7 @@
       <c r="E242" t="n">
         <v>58.782575370465</v>
       </c>
-      <c r="F242" t="b">
+      <c r="F242" t="n">
         <v>0</v>
       </c>
       <c r="G242" t="inlineStr">
@@ -6510,7 +6510,7 @@
       <c r="E243" t="n">
         <v>19.03951305065512</v>
       </c>
-      <c r="F243" t="b">
+      <c r="F243" t="n">
         <v>0</v>
       </c>
       <c r="G243" t="inlineStr">
@@ -6535,7 +6535,7 @@
       <c r="E244" t="n">
         <v>34.19245442984315</v>
       </c>
-      <c r="F244" t="b">
+      <c r="F244" t="n">
         <v>0</v>
       </c>
       <c r="G244" t="inlineStr">
@@ -6560,7 +6560,7 @@
       <c r="E245" t="n">
         <v>29.21455938697317</v>
       </c>
-      <c r="F245" t="b">
+      <c r="F245" t="n">
         <v>0</v>
       </c>
       <c r="G245" t="inlineStr">
@@ -6585,7 +6585,7 @@
       <c r="E246" t="n">
         <v>73.57155597835781</v>
       </c>
-      <c r="F246" t="b">
+      <c r="F246" t="n">
         <v>0</v>
       </c>
       <c r="G246" t="inlineStr">
@@ -6610,7 +6610,7 @@
       <c r="E247" t="n">
         <v>7.757389878906462</v>
       </c>
-      <c r="F247" t="b">
+      <c r="F247" t="n">
         <v>0</v>
       </c>
       <c r="G247" t="inlineStr">
@@ -6635,7 +6635,7 @@
       <c r="E248" t="n">
         <v>79.03719627385838</v>
       </c>
-      <c r="F248" t="b">
+      <c r="F248" t="n">
         <v>0</v>
       </c>
       <c r="G248" t="inlineStr">
@@ -6660,7 +6660,7 @@
       <c r="E249" t="n">
         <v>-5.250344024558062</v>
       </c>
-      <c r="F249" t="b">
+      <c r="F249" t="n">
         <v>0</v>
       </c>
       <c r="G249" t="inlineStr">
@@ -6685,7 +6685,7 @@
       <c r="E250" t="n">
         <v>-3.74527501349996</v>
       </c>
-      <c r="F250" t="b">
+      <c r="F250" t="n">
         <v>0</v>
       </c>
       <c r="G250" t="inlineStr">
@@ -6710,7 +6710,7 @@
       <c r="E251" t="n">
         <v>47.65738498789347</v>
       </c>
-      <c r="F251" t="b">
+      <c r="F251" t="n">
         <v>0</v>
       </c>
       <c r="G251" t="inlineStr">
@@ -6735,7 +6735,7 @@
       <c r="E252" t="n">
         <v>-4.167019564665031</v>
       </c>
-      <c r="F252" t="b">
+      <c r="F252" t="n">
         <v>0</v>
       </c>
       <c r="G252" t="inlineStr">
@@ -6760,7 +6760,7 @@
       <c r="E253" t="n">
         <v>18.98427401981904</v>
       </c>
-      <c r="F253" t="b">
+      <c r="F253" t="n">
         <v>0</v>
       </c>
       <c r="G253" t="inlineStr">
@@ -6785,7 +6785,7 @@
       <c r="E254" t="n">
         <v>18.32736634619252</v>
       </c>
-      <c r="F254" t="b">
+      <c r="F254" t="n">
         <v>0</v>
       </c>
       <c r="G254" t="inlineStr">
@@ -6810,7 +6810,7 @@
       <c r="E255" t="n">
         <v>35.9058803137323</v>
       </c>
-      <c r="F255" t="b">
+      <c r="F255" t="n">
         <v>0</v>
       </c>
       <c r="G255" t="inlineStr">
@@ -6835,7 +6835,7 @@
       <c r="E256" t="n">
         <v>-5.316527672479154</v>
       </c>
-      <c r="F256" t="b">
+      <c r="F256" t="n">
         <v>0</v>
       </c>
       <c r="G256" t="inlineStr">
@@ -6860,7 +6860,7 @@
       <c r="E257" t="n">
         <v>6.312083024462556</v>
       </c>
-      <c r="F257" t="b">
+      <c r="F257" t="n">
         <v>0</v>
       </c>
       <c r="G257" t="inlineStr">
@@ -6885,7 +6885,7 @@
       <c r="E258" t="n">
         <v>6.367964923098013</v>
       </c>
-      <c r="F258" t="b">
+      <c r="F258" t="n">
         <v>0</v>
       </c>
       <c r="G258" t="inlineStr">
@@ -6910,7 +6910,7 @@
       <c r="E259" t="n">
         <v>22.90214937677888</v>
       </c>
-      <c r="F259" t="b">
+      <c r="F259" t="n">
         <v>0</v>
       </c>
       <c r="G259" t="inlineStr">
@@ -6935,7 +6935,7 @@
       <c r="E260" t="n">
         <v>0.9023431814874083</v>
       </c>
-      <c r="F260" t="b">
+      <c r="F260" t="n">
         <v>0</v>
       </c>
       <c r="G260" t="inlineStr">
@@ -6960,7 +6960,7 @@
       <c r="E261" t="n">
         <v>23.79249990690053</v>
       </c>
-      <c r="F261" t="b">
+      <c r="F261" t="n">
         <v>0</v>
       </c>
       <c r="G261" t="inlineStr">
@@ -6985,7 +6985,7 @@
       <c r="E262" t="n">
         <v>19.75956722099779</v>
       </c>
-      <c r="F262" t="b">
+      <c r="F262" t="n">
         <v>0</v>
       </c>
       <c r="G262" t="inlineStr">
@@ -7010,7 +7010,7 @@
       <c r="E263" t="n">
         <v>8.420448489320709</v>
       </c>
-      <c r="F263" t="b">
+      <c r="F263" t="n">
         <v>0</v>
       </c>
       <c r="G263" t="inlineStr">
@@ -7035,7 +7035,7 @@
       <c r="E264" t="n">
         <v>21.31241714538223</v>
       </c>
-      <c r="F264" t="b">
+      <c r="F264" t="n">
         <v>0</v>
       </c>
       <c r="G264" t="inlineStr">
@@ -7060,7 +7060,7 @@
       <c r="E265" t="n">
         <v>6.323269813968224</v>
       </c>
-      <c r="F265" t="b">
+      <c r="F265" t="n">
         <v>0</v>
       </c>
       <c r="G265" t="inlineStr">
@@ -7085,7 +7085,7 @@
       <c r="E266" t="n">
         <v>13.9146693863675</v>
       </c>
-      <c r="F266" t="b">
+      <c r="F266" t="n">
         <v>0</v>
       </c>
       <c r="G266" t="inlineStr">
@@ -7110,7 +7110,7 @@
       <c r="E267" t="n">
         <v>9.983101106399261</v>
       </c>
-      <c r="F267" t="b">
+      <c r="F267" t="n">
         <v>0</v>
       </c>
       <c r="G267" t="inlineStr">
@@ -7135,7 +7135,7 @@
       <c r="E268" t="n">
         <v>15.64407967170454</v>
       </c>
-      <c r="F268" t="b">
+      <c r="F268" t="n">
         <v>0</v>
       </c>
       <c r="G268" t="inlineStr">
@@ -7160,7 +7160,7 @@
       <c r="E269" t="n">
         <v>19.93515322664994</v>
       </c>
-      <c r="F269" t="b">
+      <c r="F269" t="n">
         <v>0</v>
       </c>
       <c r="G269" t="inlineStr">
@@ -7185,7 +7185,7 @@
       <c r="E270" t="n">
         <v>8.501867834600031</v>
       </c>
-      <c r="F270" t="b">
+      <c r="F270" t="n">
         <v>0</v>
       </c>
       <c r="G270" t="inlineStr">
@@ -7210,7 +7210,7 @@
       <c r="E271" t="n">
         <v>17.99560790576962</v>
       </c>
-      <c r="F271" t="b">
+      <c r="F271" t="n">
         <v>0</v>
       </c>
       <c r="G271" t="inlineStr">
@@ -7235,7 +7235,7 @@
       <c r="E272" t="n">
         <v>12.63161690465888</v>
       </c>
-      <c r="F272" t="b">
+      <c r="F272" t="n">
         <v>0</v>
       </c>
       <c r="G272" t="inlineStr">
@@ -7260,7 +7260,7 @@
       <c r="E273" t="n">
         <v>0.09024727754045614</v>
       </c>
-      <c r="F273" t="b">
+      <c r="F273" t="n">
         <v>0</v>
       </c>
       <c r="G273" t="inlineStr">
@@ -7285,7 +7285,7 @@
       <c r="E274" t="n">
         <v>12.95255303486582</v>
       </c>
-      <c r="F274" t="b">
+      <c r="F274" t="n">
         <v>0</v>
       </c>
       <c r="G274" t="inlineStr">
@@ -7310,7 +7310,7 @@
       <c r="E275" t="n">
         <v>16.45933376186335</v>
       </c>
-      <c r="F275" t="b">
+      <c r="F275" t="n">
         <v>0</v>
       </c>
       <c r="G275" t="inlineStr">
@@ -7335,7 +7335,7 @@
       <c r="E276" t="n">
         <v>4.454886533347913</v>
       </c>
-      <c r="F276" t="b">
+      <c r="F276" t="n">
         <v>0</v>
       </c>
       <c r="G276" t="inlineStr">
@@ -7360,7 +7360,7 @@
       <c r="E277" t="n">
         <v>13.54618986802896</v>
       </c>
-      <c r="F277" t="b">
+      <c r="F277" t="n">
         <v>0</v>
       </c>
       <c r="G277" t="inlineStr">
@@ -7385,7 +7385,7 @@
       <c r="E278" t="n">
         <v>4.992837531335792</v>
       </c>
-      <c r="F278" t="b">
+      <c r="F278" t="n">
         <v>0</v>
       </c>
       <c r="G278" t="inlineStr">
@@ -7410,7 +7410,7 @@
       <c r="E279" t="n">
         <v>8.473937496376172</v>
       </c>
-      <c r="F279" t="b">
+      <c r="F279" t="n">
         <v>0</v>
       </c>
       <c r="G279" t="inlineStr">
@@ -7435,7 +7435,7 @@
       <c r="E280" t="n">
         <v>3.715884830650285</v>
       </c>
-      <c r="F280" t="b">
+      <c r="F280" t="n">
         <v>0</v>
       </c>
       <c r="G280" t="inlineStr">
@@ -7460,7 +7460,7 @@
       <c r="E281" t="n">
         <v>7.988139879654654</v>
       </c>
-      <c r="F281" t="b">
+      <c r="F281" t="n">
         <v>0</v>
       </c>
       <c r="G281" t="inlineStr">
@@ -7485,7 +7485,7 @@
       <c r="E282" t="n">
         <v>8.295737860619724</v>
       </c>
-      <c r="F282" t="b">
+      <c r="F282" t="n">
         <v>0</v>
       </c>
       <c r="G282" t="inlineStr">
@@ -7510,7 +7510,7 @@
       <c r="E283" t="n">
         <v>-3.113156469951273</v>
       </c>
-      <c r="F283" t="b">
+      <c r="F283" t="n">
         <v>0</v>
       </c>
       <c r="G283" t="inlineStr">
@@ -7535,7 +7535,7 @@
       <c r="E284" t="n">
         <v>9.943973107091409</v>
       </c>
-      <c r="F284" t="b">
+      <c r="F284" t="n">
         <v>0</v>
       </c>
       <c r="G284" t="inlineStr">
@@ -7560,7 +7560,7 @@
       <c r="E285" t="n">
         <v>16.32303438326521</v>
       </c>
-      <c r="F285" t="b">
+      <c r="F285" t="n">
         <v>0</v>
       </c>
       <c r="G285" t="inlineStr">
@@ -7585,7 +7585,7 @@
       <c r="E286" t="n">
         <v>0.1392303818467333</v>
       </c>
-      <c r="F286" t="b">
+      <c r="F286" t="n">
         <v>0</v>
       </c>
       <c r="G286" t="inlineStr">
@@ -7610,7 +7610,7 @@
       <c r="E287" t="n">
         <v>-0.727272727272732</v>
       </c>
-      <c r="F287" t="b">
+      <c r="F287" t="n">
         <v>0</v>
       </c>
       <c r="G287" t="inlineStr">
@@ -7635,7 +7635,7 @@
       <c r="E288" t="n">
         <v>12.24368810154832</v>
       </c>
-      <c r="F288" t="b">
+      <c r="F288" t="n">
         <v>0</v>
       </c>
       <c r="G288" t="inlineStr">
@@ -7660,7 +7660,7 @@
       <c r="E289" t="n">
         <v>3.906718656268748</v>
       </c>
-      <c r="F289" t="b">
+      <c r="F289" t="n">
         <v>0</v>
       </c>
       <c r="G289" t="inlineStr">
@@ -7685,7 +7685,7 @@
       <c r="E290" t="n">
         <v>11.23333617577669</v>
       </c>
-      <c r="F290" t="b">
+      <c r="F290" t="n">
         <v>0</v>
       </c>
       <c r="G290" t="inlineStr">
@@ -7710,7 +7710,7 @@
       <c r="E291" t="n">
         <v>-1.312237752893075</v>
       </c>
-      <c r="F291" t="b">
+      <c r="F291" t="n">
         <v>0</v>
       </c>
       <c r="G291" t="inlineStr">
@@ -7735,7 +7735,7 @@
       <c r="E292" t="n">
         <v>5.079276773296248</v>
       </c>
-      <c r="F292" t="b">
+      <c r="F292" t="n">
         <v>0</v>
       </c>
       <c r="G292" t="inlineStr">
@@ -7760,7 +7760,7 @@
       <c r="E293" t="n">
         <v>7.51568009906054</v>
       </c>
-      <c r="F293" t="b">
+      <c r="F293" t="n">
         <v>0</v>
       </c>
       <c r="G293" t="inlineStr">
@@ -7785,7 +7785,7 @@
       <c r="E294" t="n">
         <v>0.2494038972784773</v>
       </c>
-      <c r="F294" t="b">
+      <c r="F294" t="n">
         <v>0</v>
       </c>
       <c r="G294" t="inlineStr">
@@ -7810,7 +7810,7 @@
       <c r="E295" t="n">
         <v>16.27200335289187</v>
       </c>
-      <c r="F295" t="b">
+      <c r="F295" t="n">
         <v>0</v>
       </c>
       <c r="G295" t="inlineStr">
@@ -7835,7 +7835,7 @@
       <c r="E296" t="n">
         <v>4.64168195451502</v>
       </c>
-      <c r="F296" t="b">
+      <c r="F296" t="n">
         <v>0</v>
       </c>
       <c r="G296" t="inlineStr">
@@ -7860,7 +7860,7 @@
       <c r="E297" t="n">
         <v>6.480117820324005</v>
       </c>
-      <c r="F297" t="b">
+      <c r="F297" t="n">
         <v>0</v>
       </c>
       <c r="G297" t="inlineStr">
@@ -7885,7 +7885,7 @@
       <c r="E298" t="n">
         <v>12.84463377115135</v>
       </c>
-      <c r="F298" t="b">
+      <c r="F298" t="n">
         <v>0</v>
       </c>
       <c r="G298" t="inlineStr">
@@ -7910,7 +7910,7 @@
       <c r="E299" t="n">
         <v>7.937598116169542</v>
       </c>
-      <c r="F299" t="b">
+      <c r="F299" t="n">
         <v>0</v>
       </c>
       <c r="G299" t="inlineStr">
@@ -7935,7 +7935,7 @@
       <c r="E300" t="n">
         <v>-1.370118370770812</v>
       </c>
-      <c r="F300" t="b">
+      <c r="F300" t="n">
         <v>0</v>
       </c>
       <c r="G300" t="inlineStr">
@@ -7960,7 +7960,7 @@
       <c r="E301" t="n">
         <v>13.07642346828317</v>
       </c>
-      <c r="F301" t="b">
+      <c r="F301" t="n">
         <v>0</v>
       </c>
       <c r="G301" t="inlineStr">
@@ -7985,7 +7985,7 @@
       <c r="E302" t="n">
         <v>5.736846140086382</v>
       </c>
-      <c r="F302" t="b">
+      <c r="F302" t="n">
         <v>0</v>
       </c>
       <c r="G302" t="inlineStr">
@@ -8010,7 +8010,7 @@
       <c r="E303" t="n">
         <v>11.37951578833343</v>
       </c>
-      <c r="F303" t="b">
+      <c r="F303" t="n">
         <v>0</v>
       </c>
       <c r="G303" t="inlineStr">
@@ -8035,7 +8035,7 @@
       <c r="E304" t="n">
         <v>9.294260906395602</v>
       </c>
-      <c r="F304" t="b">
+      <c r="F304" t="n">
         <v>0</v>
       </c>
       <c r="G304" t="inlineStr">
@@ -8060,7 +8060,7 @@
       <c r="E305" t="n">
         <v>-0.7310783405523158</v>
       </c>
-      <c r="F305" t="b">
+      <c r="F305" t="n">
         <v>0</v>
       </c>
       <c r="G305" t="inlineStr">
@@ -8085,7 +8085,7 @@
       <c r="E306" t="n">
         <v>1.320465853791908</v>
       </c>
-      <c r="F306" t="b">
+      <c r="F306" t="n">
         <v>0</v>
       </c>
       <c r="G306" t="inlineStr">
@@ -8110,7 +8110,7 @@
       <c r="E307" t="n">
         <v>4.830134270523567</v>
       </c>
-      <c r="F307" t="b">
+      <c r="F307" t="n">
         <v>0</v>
       </c>
       <c r="G307" t="inlineStr">
@@ -8135,7 +8135,7 @@
       <c r="E308" t="n">
         <v>13.20161402532349</v>
       </c>
-      <c r="F308" t="b">
+      <c r="F308" t="n">
         <v>0</v>
       </c>
       <c r="G308" t="inlineStr">
@@ -8160,7 +8160,7 @@
       <c r="E309" t="n">
         <v>67.73191623595642</v>
       </c>
-      <c r="F309" t="b">
+      <c r="F309" t="n">
         <v>0</v>
       </c>
       <c r="G309" t="inlineStr">
@@ -8185,7 +8185,7 @@
       <c r="E310" t="n">
         <v>4.464426152152257</v>
       </c>
-      <c r="F310" t="b">
+      <c r="F310" t="n">
         <v>0</v>
       </c>
       <c r="G310" t="inlineStr">
@@ -8210,7 +8210,7 @@
       <c r="E311" t="n">
         <v>7.696270036057329</v>
       </c>
-      <c r="F311" t="b">
+      <c r="F311" t="n">
         <v>0</v>
       </c>
       <c r="G311" t="inlineStr">
@@ -8235,7 +8235,7 @@
       <c r="E312" t="n">
         <v>3.266553266553274</v>
       </c>
-      <c r="F312" t="b">
+      <c r="F312" t="n">
         <v>0</v>
       </c>
       <c r="G312" t="inlineStr">
@@ -8260,7 +8260,7 @@
       <c r="E313" t="n">
         <v>-0.4563150169123786</v>
       </c>
-      <c r="F313" t="b">
+      <c r="F313" t="n">
         <v>0</v>
       </c>
       <c r="G313" t="inlineStr">
@@ -8285,7 +8285,7 @@
       <c r="E314" t="n">
         <v>12.54531393494127</v>
       </c>
-      <c r="F314" t="b">
+      <c r="F314" t="n">
         <v>0</v>
       </c>
       <c r="G314" t="inlineStr">
@@ -8310,7 +8310,7 @@
       <c r="E315" t="n">
         <v>24.12468391363547</v>
       </c>
-      <c r="F315" t="b">
+      <c r="F315" t="n">
         <v>0</v>
       </c>
       <c r="G315" t="inlineStr">
@@ -8335,7 +8335,7 @@
       <c r="E316" t="n">
         <v>1.70755928016082</v>
       </c>
-      <c r="F316" t="b">
+      <c r="F316" t="n">
         <v>0</v>
       </c>
       <c r="G316" t="inlineStr">
@@ -8360,7 +8360,7 @@
       <c r="E317" t="n">
         <v>2.522131705717667</v>
       </c>
-      <c r="F317" t="b">
+      <c r="F317" t="n">
         <v>0</v>
       </c>
       <c r="G317" t="inlineStr">
@@ -8385,7 +8385,7 @@
       <c r="E318" t="n">
         <v>18.17813874423248</v>
       </c>
-      <c r="F318" t="b">
+      <c r="F318" t="n">
         <v>0</v>
       </c>
       <c r="G318" t="inlineStr">
@@ -8410,7 +8410,7 @@
       <c r="E319" t="n">
         <v>0.6533138485343315</v>
       </c>
-      <c r="F319" t="b">
+      <c r="F319" t="n">
         <v>0</v>
       </c>
       <c r="G319" t="inlineStr">
@@ -8435,7 +8435,7 @@
       <c r="E320" t="n">
         <v>23.84276899628801</v>
       </c>
-      <c r="F320" t="b">
+      <c r="F320" t="n">
         <v>0</v>
       </c>
       <c r="G320" t="inlineStr">
@@ -8460,7 +8460,7 @@
       <c r="E321" t="n">
         <v>-32.47207916208554</v>
       </c>
-      <c r="F321" t="b">
+      <c r="F321" t="n">
         <v>0</v>
       </c>
       <c r="G321" t="inlineStr">
@@ -8485,7 +8485,7 @@
       <c r="E322" t="n">
         <v>-4.005119325453588</v>
       </c>
-      <c r="F322" t="b">
+      <c r="F322" t="n">
         <v>0</v>
       </c>
       <c r="G322" t="inlineStr">
@@ -8510,7 +8510,7 @@
       <c r="E323" t="n">
         <v>8.733083870241675</v>
       </c>
-      <c r="F323" t="b">
+      <c r="F323" t="n">
         <v>0</v>
       </c>
       <c r="G323" t="inlineStr">
@@ -8535,7 +8535,7 @@
       <c r="E324" t="n">
         <v>9.483573803495716</v>
       </c>
-      <c r="F324" t="b">
+      <c r="F324" t="n">
         <v>0</v>
       </c>
       <c r="G324" t="inlineStr">
@@ -8560,7 +8560,7 @@
       <c r="E325" t="n">
         <v>14.97034781214939</v>
       </c>
-      <c r="F325" t="b">
+      <c r="F325" t="n">
         <v>0</v>
       </c>
       <c r="G325" t="inlineStr">
@@ -8585,7 +8585,7 @@
       <c r="E326" t="n">
         <v>13.28136743327106</v>
       </c>
-      <c r="F326" t="b">
+      <c r="F326" t="n">
         <v>0</v>
       </c>
       <c r="G326" t="inlineStr">
@@ -8610,7 +8610,7 @@
       <c r="E327" t="n">
         <v>10.58178256611166</v>
       </c>
-      <c r="F327" t="b">
+      <c r="F327" t="n">
         <v>0</v>
       </c>
       <c r="G327" t="inlineStr">
@@ -8635,7 +8635,7 @@
       <c r="E328" t="n">
         <v>12.28329205562964</v>
       </c>
-      <c r="F328" t="b">
+      <c r="F328" t="n">
         <v>0</v>
       </c>
       <c r="G328" t="inlineStr">
@@ -8660,7 +8660,7 @@
       <c r="E329" t="n">
         <v>39.77711628822358</v>
       </c>
-      <c r="F329" t="b">
+      <c r="F329" t="n">
         <v>0</v>
       </c>
       <c r="G329" t="inlineStr">
@@ -8685,7 +8685,7 @@
       <c r="E330" t="n">
         <v>18.39581716060095</v>
       </c>
-      <c r="F330" t="b">
+      <c r="F330" t="n">
         <v>0</v>
       </c>
       <c r="G330" t="inlineStr">
@@ -8710,7 +8710,7 @@
       <c r="E331" t="n">
         <v>25.67825319554757</v>
       </c>
-      <c r="F331" t="b">
+      <c r="F331" t="n">
         <v>0</v>
       </c>
       <c r="G331" t="inlineStr">
@@ -8735,7 +8735,7 @@
       <c r="E332" t="n">
         <v>12.26130453769503</v>
       </c>
-      <c r="F332" t="b">
+      <c r="F332" t="n">
         <v>0</v>
       </c>
       <c r="G332" t="inlineStr">
@@ -8760,7 +8760,7 @@
       <c r="E333" t="n">
         <v>14.28510218946828</v>
       </c>
-      <c r="F333" t="b">
+      <c r="F333" t="n">
         <v>0</v>
       </c>
       <c r="G333" t="inlineStr">
@@ -8785,7 +8785,7 @@
       <c r="E334" t="n">
         <v>24.52618095312786</v>
       </c>
-      <c r="F334" t="b">
+      <c r="F334" t="n">
         <v>0</v>
       </c>
       <c r="G334" t="inlineStr">
@@ -8810,7 +8810,7 @@
       <c r="E335" t="n">
         <v>17.84355836158047</v>
       </c>
-      <c r="F335" t="b">
+      <c r="F335" t="n">
         <v>0</v>
       </c>
       <c r="G335" t="inlineStr">
@@ -8835,7 +8835,7 @@
       <c r="E336" t="n">
         <v>11.89958765184442</v>
       </c>
-      <c r="F336" t="b">
+      <c r="F336" t="n">
         <v>0</v>
       </c>
       <c r="G336" t="inlineStr">
@@ -8860,7 +8860,7 @@
       <c r="E337" t="n">
         <v>9.789488359124498</v>
       </c>
-      <c r="F337" t="b">
+      <c r="F337" t="n">
         <v>0</v>
       </c>
       <c r="G337" t="inlineStr">
@@ -8885,7 +8885,7 @@
       <c r="E338" t="n">
         <v>11.65598817151306</v>
       </c>
-      <c r="F338" t="b">
+      <c r="F338" t="n">
         <v>0</v>
       </c>
       <c r="G338" t="inlineStr">
@@ -8910,7 +8910,7 @@
       <c r="E339" t="n">
         <v>4.366541486572673</v>
       </c>
-      <c r="F339" t="b">
+      <c r="F339" t="n">
         <v>0</v>
       </c>
       <c r="G339" t="inlineStr">
@@ -8935,7 +8935,7 @@
       <c r="E340" t="n">
         <v>4.636267232237534</v>
       </c>
-      <c r="F340" t="b">
+      <c r="F340" t="n">
         <v>0</v>
       </c>
       <c r="G340" t="inlineStr">
@@ -8960,7 +8960,7 @@
       <c r="E341" t="n">
         <v>-0.7233623147594126</v>
       </c>
-      <c r="F341" t="b">
+      <c r="F341" t="n">
         <v>0</v>
       </c>
       <c r="G341" t="inlineStr">
@@ -8985,7 +8985,7 @@
       <c r="E342" t="n">
         <v>-0.5746793944653383</v>
       </c>
-      <c r="F342" t="b">
+      <c r="F342" t="n">
         <v>0</v>
       </c>
       <c r="G342" t="inlineStr">
@@ -9010,7 +9010,7 @@
       <c r="E343" t="n">
         <v>-3.569891498856093</v>
       </c>
-      <c r="F343" t="b">
+      <c r="F343" t="n">
         <v>0</v>
       </c>
       <c r="G343" t="inlineStr">
@@ -9035,7 +9035,7 @@
       <c r="E344" t="n">
         <v>6.241711608169043</v>
       </c>
-      <c r="F344" t="b">
+      <c r="F344" t="n">
         <v>0</v>
       </c>
       <c r="G344" t="inlineStr">
@@ -9060,7 +9060,7 @@
       <c r="E345" t="n">
         <v>14.67214036666291</v>
       </c>
-      <c r="F345" t="b">
+      <c r="F345" t="n">
         <v>0</v>
       </c>
       <c r="G345" t="inlineStr">
@@ -9085,7 +9085,7 @@
       <c r="E346" t="n">
         <v>17.50393618137924</v>
       </c>
-      <c r="F346" t="b">
+      <c r="F346" t="n">
         <v>0</v>
       </c>
       <c r="G346" t="inlineStr">
@@ -9110,7 +9110,7 @@
       <c r="E347" t="n">
         <v>7.891443251432717</v>
       </c>
-      <c r="F347" t="b">
+      <c r="F347" t="n">
         <v>0</v>
       </c>
       <c r="G347" t="inlineStr">
@@ -9135,7 +9135,7 @@
       <c r="E348" t="n">
         <v>16.45544406543335</v>
       </c>
-      <c r="F348" t="b">
+      <c r="F348" t="n">
         <v>0</v>
       </c>
       <c r="G348" t="inlineStr">
@@ -9160,7 +9160,7 @@
       <c r="E349" t="n">
         <v>18.20398212108898</v>
       </c>
-      <c r="F349" t="b">
+      <c r="F349" t="n">
         <v>0</v>
       </c>
       <c r="G349" t="inlineStr">
@@ -9185,7 +9185,7 @@
       <c r="E350" t="n">
         <v>25.22112625842487</v>
       </c>
-      <c r="F350" t="b">
+      <c r="F350" t="n">
         <v>0</v>
       </c>
       <c r="G350" t="inlineStr">
@@ -9210,7 +9210,7 @@
       <c r="E351" t="n">
         <v>8.65285062036425</v>
       </c>
-      <c r="F351" t="b">
+      <c r="F351" t="n">
         <v>0</v>
       </c>
       <c r="G351" t="inlineStr">
@@ -9235,7 +9235,7 @@
       <c r="E352" t="n">
         <v>20.34011675044592</v>
       </c>
-      <c r="F352" t="b">
+      <c r="F352" t="n">
         <v>1</v>
       </c>
       <c r="G352" t="inlineStr">
@@ -9260,7 +9260,7 @@
       <c r="E353" t="n">
         <v>-33.42670235963622</v>
       </c>
-      <c r="F353" t="b">
+      <c r="F353" t="n">
         <v>1</v>
       </c>
       <c r="G353" t="inlineStr">
@@ -9285,7 +9285,7 @@
       <c r="E354" t="n">
         <v>-91.04874216886165</v>
       </c>
-      <c r="F354" t="b">
+      <c r="F354" t="n">
         <v>1</v>
       </c>
       <c r="G354" t="inlineStr">
@@ -9310,7 +9310,7 @@
       <c r="E355" t="n">
         <v>-87.54551220314298</v>
       </c>
-      <c r="F355" t="b">
+      <c r="F355" t="n">
         <v>1</v>
       </c>
       <c r="G355" t="inlineStr">
@@ -9335,7 +9335,7 @@
       <c r="E356" t="n">
         <v>-90.06906881917284</v>
       </c>
-      <c r="F356" t="b">
+      <c r="F356" t="n">
         <v>1</v>
       </c>
       <c r="G356" t="inlineStr">
@@ -9360,7 +9360,7 @@
       <c r="E357" t="n">
         <v>-92.8203619243784</v>
       </c>
-      <c r="F357" t="b">
+      <c r="F357" t="n">
         <v>1</v>
       </c>
       <c r="G357" t="inlineStr">
@@ -9385,7 +9385,7 @@
       <c r="E358" t="n">
         <v>-93.57011416218533</v>
       </c>
-      <c r="F358" t="b">
+      <c r="F358" t="n">
         <v>1</v>
       </c>
       <c r="G358" t="inlineStr">
@@ -9410,7 +9410,7 @@
       <c r="E359" t="n">
         <v>-92.81396910678308</v>
       </c>
-      <c r="F359" t="b">
+      <c r="F359" t="n">
         <v>1</v>
       </c>
       <c r="G359" t="inlineStr">
@@ -9435,7 +9435,7 @@
       <c r="E360" t="n">
         <v>-87.03284016077995</v>
       </c>
-      <c r="F360" t="b">
+      <c r="F360" t="n">
         <v>1</v>
       </c>
       <c r="G360" t="inlineStr">
@@ -9460,7 +9460,7 @@
       <c r="E361" t="n">
         <v>-70.2475077346167</v>
       </c>
-      <c r="F361" t="b">
+      <c r="F361" t="n">
         <v>1</v>
       </c>
       <c r="G361" t="inlineStr">
